--- a/results/components/gene_names/p5s6.xlsx
+++ b/results/components/gene_names/p5s6.xlsx
@@ -22,10 +22,10 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Psn</t>
+    <t>Ef1gamma</t>
   </si>
   <si>
-    <t>Ark</t>
+    <t>tin</t>
   </si>
 </sst>
 </file>

--- a/results/components/gene_names/p5s6.xlsx
+++ b/results/components/gene_names/p5s6.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>gene1</t>
   </si>
@@ -22,10 +22,22 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Ef1gamma</t>
-  </si>
-  <si>
-    <t>tin</t>
+    <t>Syx1A</t>
+  </si>
+  <si>
+    <t>CG32082</t>
+  </si>
+  <si>
+    <t>Sxl</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>ry</t>
+  </si>
+  <si>
+    <t>Sur</t>
   </si>
 </sst>
 </file>
@@ -357,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -376,6 +388,22 @@
         <v>3</v>
       </c>
     </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
